--- a/Avances_Proyectos_Desarrollo.xlsx
+++ b/Avances_Proyectos_Desarrollo.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\GIT\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{FA76D338-6BBF-4865-BCA2-5F2C47467C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C838C13-BC69-4F38-ACB3-A4525DBE6D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8180159-C6BA-4F8C-807D-95D747635721}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" firstSheet="1" activeTab="1" xr2:uid="{E8180159-C6BA-4F8C-807D-95D747635721}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="EN CURSO" sheetId="2" r:id="rId2"/>
+    <sheet name="FINALIZADO" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
   <si>
     <t>Proyecto</t>
   </si>
@@ -49,9 +50,6 @@
     <t>31 de agosto de 2026</t>
   </si>
   <si>
-    <t>Casetas - Validador de precios</t>
-  </si>
-  <si>
     <t>App Android</t>
   </si>
   <si>
@@ -97,17 +95,62 @@
     <t>Pendiente de sesion del viernes a las 11 am</t>
   </si>
   <si>
-    <t xml:space="preserve">Pendiente de las pruebas UAT realizada por el PM </t>
-  </si>
-  <si>
     <t>Falta firma por parte del VS y OO, revision del documento el dia Viernes 12 pm</t>
+  </si>
+  <si>
+    <t>Automatizar proceso de control de peajes (Casetas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendientes de pruebas UAT Productiva y cierre de proyecto </t>
+  </si>
+  <si>
+    <t>EN MAPA ESTRATEGICO</t>
+  </si>
+  <si>
+    <t>Desarrollo Interno / Externo</t>
+  </si>
+  <si>
+    <t>Desarrollo</t>
+  </si>
+  <si>
+    <t>Fin proyecto</t>
+  </si>
+  <si>
+    <t>Desarrollo Interno</t>
+  </si>
+  <si>
+    <t>Emanuel Simon</t>
+  </si>
+  <si>
+    <t>Jaime Comparan / Emanuel Simon</t>
+  </si>
+  <si>
+    <t>NUEVAS SOLICITUDES</t>
+  </si>
+  <si>
+    <t>Jaime Comparan</t>
+  </si>
+  <si>
+    <t>Comentarios</t>
+  </si>
+  <si>
+    <t>Terminado</t>
+  </si>
+  <si>
+    <t>El equipo de Desarrollo ya termino tanto la codificacion como su documentacion.</t>
+  </si>
+  <si>
+    <t>En espera de que el PM mencione si podemos continuar con este proyecto</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,16 +164,61 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9D08E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -138,11 +226,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -158,15 +360,87 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -181,6 +455,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -201,17 +478,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B3F171B5-C2CE-4318-BDB9-D577019128C1}" name="Tabla1" displayName="Tabla1" ref="B2:F9" totalsRowShown="0" headerRowDxfId="6" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B3F171B5-C2CE-4318-BDB9-D577019128C1}" name="Tabla1" displayName="Tabla1" ref="B2:F9" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="B2:F9" xr:uid="{B3F171B5-C2CE-4318-BDB9-D577019128C1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E9">
     <sortCondition ref="E2:E9"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E003A80D-6EA8-4CF9-B9D2-493DA9B3533D}" name="Proyecto" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{811F3554-7841-4FD2-B0A0-83924D0B40B2}" name="Fecha Final" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{CB51E5F9-6E14-42C2-ADC3-A98753E7BA08}" name="Porcentaje" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{4EA40B15-A5FA-474A-808C-8B105D5B5FBD}" name="Estatus" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{62FA5F94-2E95-4F89-9DC4-448C3917C123}" name="Observacion" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{E003A80D-6EA8-4CF9-B9D2-493DA9B3533D}" name="Proyecto" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{811F3554-7841-4FD2-B0A0-83924D0B40B2}" name="Fecha Final" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{CB51E5F9-6E14-42C2-ADC3-A98753E7BA08}" name="Porcentaje" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{4EA40B15-A5FA-474A-808C-8B105D5B5FBD}" name="Estatus" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{62FA5F94-2E95-4F89-9DC4-448C3917C123}" name="Observacion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -538,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
@@ -552,32 +829,32 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -586,72 +863,72 @@
         <v>0.1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D6" s="3">
         <v>0.26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3">
         <v>0.05</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -661,4 +938,362 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FD3EF3-DCEF-4198-9FEE-CDDD375F442E}">
+  <dimension ref="B2:L10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+    </row>
+    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="13">
+        <v>46161</v>
+      </c>
+      <c r="H3" s="13">
+        <v>46168</v>
+      </c>
+      <c r="I3" s="13">
+        <v>46175</v>
+      </c>
+      <c r="J3" s="13">
+        <v>46189</v>
+      </c>
+      <c r="K3" s="13">
+        <v>46196</v>
+      </c>
+      <c r="L3" s="13">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.18</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="8" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="16">
+        <v>46161</v>
+      </c>
+      <c r="H9" s="16">
+        <v>46168</v>
+      </c>
+      <c r="I9" s="16">
+        <v>46175</v>
+      </c>
+      <c r="J9" s="16">
+        <v>46189</v>
+      </c>
+      <c r="K9" s="16">
+        <v>46196</v>
+      </c>
+      <c r="L9" s="16">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="L10" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B8:L8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500E7C55-F0E5-4065-81F8-757C37849D3E}">
+  <dimension ref="B1:I6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" customWidth="1"/>
+    <col min="7" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="16">
+        <v>46161</v>
+      </c>
+      <c r="H3" s="16">
+        <v>46168</v>
+      </c>
+      <c r="I3" s="16">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="H4" s="19">
+        <v>1</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="H5" s="23">
+        <v>1</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>